--- a/Experiment/Orders/PAR17_RUN06.xlsx
+++ b/Experiment/Orders/PAR17_RUN06.xlsx
@@ -27,315 +27,315 @@
     <t>3D_Object</t>
   </si>
   <si>
+    <t>3D_Face</t>
+  </si>
+  <si>
+    <t>2D_Face</t>
+  </si>
+  <si>
+    <t>3D_Hand</t>
+  </si>
+  <si>
     <t>2D_Hand</t>
   </si>
   <si>
-    <t>3D_Hand</t>
-  </si>
-  <si>
     <t>2D_Object</t>
   </si>
   <si>
-    <t>3D_Face</t>
-  </si>
-  <si>
-    <t>2D_Face</t>
-  </si>
-  <si>
     <t>Duration_Seconds</t>
   </si>
   <si>
     <t>Filename_left</t>
   </si>
   <si>
+    <t>Object_07_L.png</t>
+  </si>
+  <si>
+    <t>Face_16_L.png</t>
+  </si>
+  <si>
+    <t>Face_09_L.png</t>
+  </si>
+  <si>
+    <t>Face_05_R.png</t>
+  </si>
+  <si>
+    <t>Hand_07_L.png</t>
+  </si>
+  <si>
+    <t>Hand_07_R.png</t>
+  </si>
+  <si>
+    <t>Object_07_R.png</t>
+  </si>
+  <si>
+    <t>Hand_08_L.png</t>
+  </si>
+  <si>
+    <t>Object_14_R.png</t>
+  </si>
+  <si>
+    <t>Object_03_L.png</t>
+  </si>
+  <si>
+    <t>Hand_14_R.png</t>
+  </si>
+  <si>
+    <t>Hand_12_R.png</t>
+  </si>
+  <si>
+    <t>Object_06_L.png</t>
+  </si>
+  <si>
+    <t>Face_09_R.png</t>
+  </si>
+  <si>
+    <t>Hand_05_R.png</t>
+  </si>
+  <si>
+    <t>Hand_10_L.png</t>
+  </si>
+  <si>
+    <t>Face_07_L.png</t>
+  </si>
+  <si>
+    <t>Object_01_R.png</t>
+  </si>
+  <si>
+    <t>Face_12_R.png</t>
+  </si>
+  <si>
+    <t>Face_12_L.png</t>
+  </si>
+  <si>
+    <t>Hand_13_R.png</t>
+  </si>
+  <si>
+    <t>Face_04_R.png</t>
+  </si>
+  <si>
+    <t>Object_01_L.png</t>
+  </si>
+  <si>
+    <t>Hand_02_L.png</t>
+  </si>
+  <si>
+    <t>Hand_12_L.png</t>
+  </si>
+  <si>
+    <t>Object_08_L.png</t>
+  </si>
+  <si>
+    <t>Object_04_L.png</t>
+  </si>
+  <si>
+    <t>Object_13_R.png</t>
+  </si>
+  <si>
+    <t>Face_15_L.png</t>
+  </si>
+  <si>
+    <t>Hand_01_L.png</t>
+  </si>
+  <si>
+    <t>Face_11_R.png</t>
+  </si>
+  <si>
+    <t>Object_15_R.png</t>
+  </si>
+  <si>
+    <t>Object_06_R.png</t>
+  </si>
+  <si>
+    <t>Hand_01_R.png</t>
+  </si>
+  <si>
+    <t>Face_10_L.png</t>
+  </si>
+  <si>
+    <t>Object_16_L.png</t>
+  </si>
+  <si>
+    <t>Object_12_R.png</t>
+  </si>
+  <si>
+    <t>Face_14_L.png</t>
+  </si>
+  <si>
+    <t>Object_10_R.png</t>
+  </si>
+  <si>
+    <t>Object_09_R.png</t>
+  </si>
+  <si>
+    <t>Object_13_L.png</t>
+  </si>
+  <si>
+    <t>Object_11_L.png</t>
+  </si>
+  <si>
+    <t>Hand_11_R.png</t>
+  </si>
+  <si>
+    <t>Face_02_R.png</t>
+  </si>
+  <si>
+    <t>Face_01_R.png</t>
+  </si>
+  <si>
+    <t>Face_10_R.png</t>
+  </si>
+  <si>
+    <t>Hand_16_R.png</t>
+  </si>
+  <si>
+    <t>Hand_15_L.png</t>
+  </si>
+  <si>
+    <t>Face_11_L.png</t>
+  </si>
+  <si>
+    <t>Hand_06_L.png</t>
+  </si>
+  <si>
+    <t>Hand_13_L.png</t>
+  </si>
+  <si>
+    <t>Face_08_R.png</t>
+  </si>
+  <si>
+    <t>Object_12_L.png</t>
+  </si>
+  <si>
+    <t>Face_01_L.png</t>
+  </si>
+  <si>
+    <t>Face_13_R.png</t>
+  </si>
+  <si>
+    <t>Hand_04_L.png</t>
+  </si>
+  <si>
+    <t>Hand_02_R.png</t>
+  </si>
+  <si>
+    <t>Object_02_L.png</t>
+  </si>
+  <si>
+    <t>Face_07_R.png</t>
+  </si>
+  <si>
+    <t>Face_05_L.png</t>
+  </si>
+  <si>
+    <t>Object_09_L.png</t>
+  </si>
+  <si>
+    <t>Hand_05_L.png</t>
+  </si>
+  <si>
+    <t>Object_03_R.png</t>
+  </si>
+  <si>
+    <t>Hand_09_L.png</t>
+  </si>
+  <si>
+    <t>Object_14_L.png</t>
+  </si>
+  <si>
+    <t>Face_06_R.png</t>
+  </si>
+  <si>
+    <t>Object_04_R.png</t>
+  </si>
+  <si>
+    <t>Face_14_R.png</t>
+  </si>
+  <si>
+    <t>Hand_11_L.png</t>
+  </si>
+  <si>
+    <t>Object_11_R.png</t>
+  </si>
+  <si>
+    <t>Hand_09_R.png</t>
+  </si>
+  <si>
+    <t>Face_04_L.png</t>
+  </si>
+  <si>
+    <t>Hand_06_R.png</t>
+  </si>
+  <si>
+    <t>Object_08_R.png</t>
+  </si>
+  <si>
+    <t>Hand_03_L.png</t>
+  </si>
+  <si>
+    <t>Hand_08_R.png</t>
+  </si>
+  <si>
+    <t>Hand_04_R.png</t>
+  </si>
+  <si>
+    <t>Hand_14_L.png</t>
+  </si>
+  <si>
+    <t>Face_13_L.png</t>
+  </si>
+  <si>
+    <t>Face_08_L.png</t>
+  </si>
+  <si>
+    <t>Object_05_L.png</t>
+  </si>
+  <si>
+    <t>Face_02_L.png</t>
+  </si>
+  <si>
+    <t>Hand_03_R.png</t>
+  </si>
+  <si>
+    <t>Object_15_L.png</t>
+  </si>
+  <si>
+    <t>Hand_15_R.png</t>
+  </si>
+  <si>
+    <t>Face_15_R.png</t>
+  </si>
+  <si>
+    <t>Object_02_R.png</t>
+  </si>
+  <si>
+    <t>Face_06_L.png</t>
+  </si>
+  <si>
+    <t>Object_16_R.png</t>
+  </si>
+  <si>
     <t>Object_10_L.png</t>
   </si>
   <si>
-    <t>Hand_11_R.png</t>
-  </si>
-  <si>
-    <t>Hand_08_L.png</t>
-  </si>
-  <si>
-    <t>Hand_16_R.png</t>
-  </si>
-  <si>
-    <t>Object_14_R.png</t>
-  </si>
-  <si>
-    <t>Hand_13_L.png</t>
-  </si>
-  <si>
-    <t>Face_15_L.png</t>
-  </si>
-  <si>
-    <t>Hand_05_L.png</t>
-  </si>
-  <si>
-    <t>Object_14_L.png</t>
-  </si>
-  <si>
-    <t>Face_10_L.png</t>
-  </si>
-  <si>
-    <t>Face_04_R.png</t>
+    <t>Object_05_R.png</t>
+  </si>
+  <si>
+    <t>Face_03_R.png</t>
+  </si>
+  <si>
+    <t>Face_03_L.png</t>
+  </si>
+  <si>
+    <t>Hand_16_L.png</t>
   </si>
   <si>
     <t>Face_16_R.png</t>
   </si>
   <si>
-    <t>Object_16_R.png</t>
-  </si>
-  <si>
-    <t>Object_10_R.png</t>
-  </si>
-  <si>
-    <t>Face_02_R.png</t>
-  </si>
-  <si>
-    <t>Hand_01_L.png</t>
-  </si>
-  <si>
-    <t>Face_05_R.png</t>
-  </si>
-  <si>
-    <t>Face_06_L.png</t>
-  </si>
-  <si>
-    <t>Object_04_R.png</t>
-  </si>
-  <si>
-    <t>Object_12_L.png</t>
-  </si>
-  <si>
-    <t>Hand_07_L.png</t>
-  </si>
-  <si>
-    <t>Hand_06_L.png</t>
-  </si>
-  <si>
-    <t>Object_01_R.png</t>
-  </si>
-  <si>
-    <t>Face_02_L.png</t>
-  </si>
-  <si>
-    <t>Face_13_L.png</t>
-  </si>
-  <si>
-    <t>Object_01_L.png</t>
-  </si>
-  <si>
-    <t>Face_07_R.png</t>
-  </si>
-  <si>
-    <t>Hand_07_R.png</t>
-  </si>
-  <si>
-    <t>Object_07_L.png</t>
-  </si>
-  <si>
-    <t>Object_06_L.png</t>
-  </si>
-  <si>
-    <t>Object_09_R.png</t>
-  </si>
-  <si>
     <t>Hand_10_R.png</t>
   </si>
   <si>
-    <t>Hand_08_R.png</t>
-  </si>
-  <si>
-    <t>Face_14_L.png</t>
-  </si>
-  <si>
-    <t>Hand_01_R.png</t>
-  </si>
-  <si>
-    <t>Face_11_R.png</t>
-  </si>
-  <si>
-    <t>Object_11_L.png</t>
-  </si>
-  <si>
-    <t>Object_06_R.png</t>
-  </si>
-  <si>
-    <t>Hand_06_R.png</t>
-  </si>
-  <si>
-    <t>Face_05_L.png</t>
-  </si>
-  <si>
-    <t>Face_16_L.png</t>
-  </si>
-  <si>
-    <t>Hand_14_R.png</t>
-  </si>
-  <si>
-    <t>Object_13_L.png</t>
-  </si>
-  <si>
-    <t>Object_05_L.png</t>
-  </si>
-  <si>
-    <t>Face_06_R.png</t>
-  </si>
-  <si>
-    <t>Face_12_L.png</t>
-  </si>
-  <si>
-    <t>Face_01_R.png</t>
-  </si>
-  <si>
-    <t>Object_16_L.png</t>
-  </si>
-  <si>
-    <t>Hand_10_L.png</t>
-  </si>
-  <si>
-    <t>Object_07_R.png</t>
-  </si>
-  <si>
-    <t>Object_15_R.png</t>
-  </si>
-  <si>
-    <t>Face_08_L.png</t>
-  </si>
-  <si>
-    <t>Hand_11_L.png</t>
-  </si>
-  <si>
-    <t>Face_03_R.png</t>
-  </si>
-  <si>
-    <t>Hand_02_R.png</t>
-  </si>
-  <si>
-    <t>Face_13_R.png</t>
-  </si>
-  <si>
-    <t>Face_12_R.png</t>
-  </si>
-  <si>
-    <t>Hand_14_L.png</t>
-  </si>
-  <si>
-    <t>Hand_09_R.png</t>
-  </si>
-  <si>
-    <t>Hand_13_R.png</t>
-  </si>
-  <si>
-    <t>Object_02_R.png</t>
-  </si>
-  <si>
-    <t>Object_02_L.png</t>
-  </si>
-  <si>
-    <t>Hand_04_R.png</t>
-  </si>
-  <si>
-    <t>Hand_04_L.png</t>
-  </si>
-  <si>
-    <t>Hand_09_L.png</t>
-  </si>
-  <si>
-    <t>Face_07_L.png</t>
-  </si>
-  <si>
-    <t>Object_03_L.png</t>
-  </si>
-  <si>
-    <t>Face_03_L.png</t>
-  </si>
-  <si>
-    <t>Object_05_R.png</t>
-  </si>
-  <si>
-    <t>Hand_03_L.png</t>
-  </si>
-  <si>
-    <t>Object_08_L.png</t>
-  </si>
-  <si>
-    <t>Face_11_L.png</t>
-  </si>
-  <si>
-    <t>Face_10_R.png</t>
-  </si>
-  <si>
-    <t>Object_03_R.png</t>
-  </si>
-  <si>
-    <t>Face_08_R.png</t>
-  </si>
-  <si>
-    <t>Hand_15_L.png</t>
-  </si>
-  <si>
-    <t>Face_04_L.png</t>
-  </si>
-  <si>
-    <t>Object_15_L.png</t>
-  </si>
-  <si>
-    <t>Hand_15_R.png</t>
-  </si>
-  <si>
-    <t>Object_09_L.png</t>
-  </si>
-  <si>
-    <t>Hand_12_L.png</t>
-  </si>
-  <si>
-    <t>Face_15_R.png</t>
-  </si>
-  <si>
-    <t>Object_13_R.png</t>
-  </si>
-  <si>
-    <t>Object_04_L.png</t>
-  </si>
-  <si>
-    <t>Object_08_R.png</t>
-  </si>
-  <si>
-    <t>Face_09_L.png</t>
-  </si>
-  <si>
-    <t>Object_12_R.png</t>
-  </si>
-  <si>
-    <t>Face_14_R.png</t>
-  </si>
-  <si>
-    <t>Hand_05_R.png</t>
-  </si>
-  <si>
-    <t>Face_01_L.png</t>
-  </si>
-  <si>
-    <t>Hand_16_L.png</t>
-  </si>
-  <si>
-    <t>Hand_03_R.png</t>
-  </si>
-  <si>
-    <t>Hand_02_L.png</t>
-  </si>
-  <si>
-    <t>Object_11_R.png</t>
-  </si>
-  <si>
-    <t>Hand_12_R.png</t>
-  </si>
-  <si>
-    <t>Face_09_R.png</t>
-  </si>
-  <si>
     <t>Filename_right</t>
   </si>
   <si>
@@ -372,64 +372,64 @@
     <t>Object</t>
   </si>
   <si>
+    <t>Face</t>
+  </si>
+  <si>
     <t>Hand</t>
   </si>
   <si>
-    <t>Face</t>
-  </si>
-  <si>
     <t>Stim</t>
   </si>
   <si>
     <t>0</t>
   </si>
   <si>
+    <t>07</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>09</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>08</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
     <t>10</t>
   </si>
   <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
     <t>11</t>
-  </si>
-  <si>
-    <t>08</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>05</t>
-  </si>
-  <si>
-    <t>04</t>
-  </si>
-  <si>
-    <t>02</t>
-  </si>
-  <si>
-    <t>01</t>
-  </si>
-  <si>
-    <t>06</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>07</t>
-  </si>
-  <si>
-    <t>09</t>
-  </si>
-  <si>
-    <t>03</t>
   </si>
 </sst>
 </file>
@@ -572,7 +572,7 @@
         <v>11</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F3" s="0" t="s">
         <v>109</v>
@@ -602,7 +602,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D4" s="0"/>
       <c r="E4" s="0"/>
@@ -636,7 +636,7 @@
         <v>12</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>12</v>
+        <v>105</v>
       </c>
       <c r="F5" s="0" t="s">
         <v>109</v>
@@ -649,7 +649,7 @@
         <v>113</v>
       </c>
       <c r="J5" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K5" s="0" t="s">
         <v>119</v>
@@ -691,7 +691,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7" s="0">
         <v>1</v>
@@ -700,7 +700,7 @@
         <v>13</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="F7" s="0" t="s">
         <v>109</v>
@@ -755,7 +755,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" s="0">
         <v>1</v>
@@ -794,7 +794,7 @@
         <v>2</v>
       </c>
       <c r="C10" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D10" s="0"/>
       <c r="E10" s="0"/>
@@ -828,7 +828,7 @@
         <v>15</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F11" s="0" t="s">
         <v>109</v>
@@ -841,13 +841,13 @@
         <v>113</v>
       </c>
       <c r="J11" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K11" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L11" s="0" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12">
@@ -858,7 +858,7 @@
         <v>2</v>
       </c>
       <c r="C12" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D12" s="0"/>
       <c r="E12" s="0"/>
@@ -883,7 +883,7 @@
         <v>6</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C13" s="0">
         <v>1</v>
@@ -892,7 +892,7 @@
         <v>16</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="F13" s="0" t="s">
         <v>109</v>
@@ -905,13 +905,13 @@
         <v>113</v>
       </c>
       <c r="J13" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K13" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L13" s="0" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -947,7 +947,7 @@
         <v>7</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C15" s="0">
         <v>1</v>
@@ -956,7 +956,7 @@
         <v>17</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>92</v>
+        <v>17</v>
       </c>
       <c r="F15" s="0" t="s">
         <v>109</v>
@@ -969,13 +969,13 @@
         <v>113</v>
       </c>
       <c r="J15" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K15" s="0" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L15" s="0" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
@@ -986,7 +986,7 @@
         <v>2</v>
       </c>
       <c r="C16" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D16" s="0"/>
       <c r="E16" s="0"/>
@@ -1011,7 +1011,7 @@
         <v>8</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C17" s="0">
         <v>1</v>
@@ -1020,7 +1020,7 @@
         <v>18</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="F17" s="0" t="s">
         <v>109</v>
@@ -1036,10 +1036,10 @@
         <v>115</v>
       </c>
       <c r="K17" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L17" s="0" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="18">
@@ -1050,7 +1050,7 @@
         <v>2</v>
       </c>
       <c r="C18" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D18" s="0"/>
       <c r="E18" s="0"/>
@@ -1075,7 +1075,7 @@
         <v>9</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C19" s="0">
         <v>1</v>
@@ -1084,7 +1084,7 @@
         <v>19</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F19" s="0" t="s">
         <v>109</v>
@@ -1097,13 +1097,13 @@
         <v>113</v>
       </c>
       <c r="J19" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K19" s="0" t="s">
         <v>118</v>
       </c>
       <c r="L19" s="0" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20">
@@ -1145,16 +1145,16 @@
         <v>1</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>15</v>
+        <v>73</v>
       </c>
       <c r="F21" s="0" t="s">
         <v>109</v>
       </c>
       <c r="G21" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" s="0"/>
       <c r="I21" s="0" t="s">
@@ -1167,7 +1167,7 @@
         <v>118</v>
       </c>
       <c r="L21" s="0" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="22">
@@ -1209,10 +1209,10 @@
         <v>1</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="F23" s="0" t="s">
         <v>109</v>
@@ -1225,13 +1225,13 @@
         <v>113</v>
       </c>
       <c r="J23" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K23" s="0" t="s">
         <v>120</v>
       </c>
       <c r="L23" s="0" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="24">
@@ -1267,16 +1267,16 @@
         <v>12</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C25" s="0">
         <v>1</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F25" s="0" t="s">
         <v>109</v>
@@ -1295,7 +1295,7 @@
         <v>120</v>
       </c>
       <c r="L25" s="0" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="26">
@@ -1331,16 +1331,16 @@
         <v>13</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C27" s="0">
         <v>1</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="F27" s="0" t="s">
         <v>109</v>
@@ -1353,13 +1353,13 @@
         <v>113</v>
       </c>
       <c r="J27" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K27" s="0" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L27" s="0" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="28">
@@ -1395,16 +1395,16 @@
         <v>14</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C29" s="0">
         <v>1</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F29" s="0" t="s">
         <v>109</v>
@@ -1420,10 +1420,10 @@
         <v>116</v>
       </c>
       <c r="K29" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L29" s="0" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30">
@@ -1434,7 +1434,7 @@
         <v>2</v>
       </c>
       <c r="C30" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D30" s="0"/>
       <c r="E30" s="0"/>
@@ -1459,16 +1459,16 @@
         <v>15</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C31" s="0">
         <v>1</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E31" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F31" s="0" t="s">
         <v>109</v>
@@ -1484,10 +1484,10 @@
         <v>116</v>
       </c>
       <c r="K31" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L31" s="0" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="32">
@@ -1523,16 +1523,16 @@
         <v>16</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C33" s="0">
         <v>1</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E33" s="0" t="s">
-        <v>25</v>
+        <v>106</v>
       </c>
       <c r="F33" s="0" t="s">
         <v>109</v>
@@ -1545,7 +1545,7 @@
         <v>113</v>
       </c>
       <c r="J33" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K33" s="0" t="s">
         <v>120</v>
@@ -1562,7 +1562,7 @@
         <v>2</v>
       </c>
       <c r="C34" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D34" s="0"/>
       <c r="E34" s="0"/>
@@ -1587,16 +1587,16 @@
         <v>17</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C35" s="0">
         <v>1</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E35" s="0" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="F35" s="0" t="s">
         <v>109</v>
@@ -1615,7 +1615,7 @@
         <v>119</v>
       </c>
       <c r="L35" s="0" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
     </row>
     <row r="36">
@@ -1657,10 +1657,10 @@
         <v>1</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E37" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F37" s="0" t="s">
         <v>109</v>
@@ -1676,10 +1676,10 @@
         <v>116</v>
       </c>
       <c r="K37" s="0" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L37" s="0" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="38">
@@ -1715,16 +1715,16 @@
         <v>19</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C39" s="0">
         <v>1</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E39" s="0" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="F39" s="0" t="s">
         <v>109</v>
@@ -1737,13 +1737,13 @@
         <v>113</v>
       </c>
       <c r="J39" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K39" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L39" s="0" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="40">
@@ -1754,7 +1754,7 @@
         <v>2</v>
       </c>
       <c r="C40" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D40" s="0"/>
       <c r="E40" s="0"/>
@@ -1779,13 +1779,13 @@
         <v>20</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C41" s="0">
         <v>1</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E41" s="0" t="s">
         <v>29</v>
@@ -1801,13 +1801,13 @@
         <v>113</v>
       </c>
       <c r="J41" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K41" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L41" s="0" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="42">
@@ -1818,7 +1818,7 @@
         <v>2</v>
       </c>
       <c r="C42" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D42" s="0"/>
       <c r="E42" s="0"/>
@@ -1843,16 +1843,16 @@
         <v>21</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C43" s="0">
         <v>1</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E43" s="0" t="s">
-        <v>97</v>
+        <v>31</v>
       </c>
       <c r="F43" s="0" t="s">
         <v>109</v>
@@ -1865,13 +1865,13 @@
         <v>113</v>
       </c>
       <c r="J43" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K43" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L43" s="0" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="44">
@@ -1882,7 +1882,7 @@
         <v>2</v>
       </c>
       <c r="C44" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D44" s="0"/>
       <c r="E44" s="0"/>
@@ -1913,10 +1913,10 @@
         <v>1</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E45" s="0" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F45" s="0" t="s">
         <v>109</v>
@@ -1929,13 +1929,13 @@
         <v>113</v>
       </c>
       <c r="J45" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K45" s="0" t="s">
         <v>119</v>
       </c>
       <c r="L45" s="0" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="46">
@@ -1971,16 +1971,16 @@
         <v>23</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C47" s="0">
         <v>1</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E47" s="0" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="F47" s="0" t="s">
         <v>109</v>
@@ -1996,10 +1996,10 @@
         <v>115</v>
       </c>
       <c r="K47" s="0" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L47" s="0" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="48">
@@ -2010,7 +2010,7 @@
         <v>2</v>
       </c>
       <c r="C48" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D48" s="0"/>
       <c r="E48" s="0"/>
@@ -2041,10 +2041,10 @@
         <v>1</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E49" s="0" t="s">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="F49" s="0" t="s">
         <v>109</v>
@@ -2057,13 +2057,13 @@
         <v>113</v>
       </c>
       <c r="J49" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K49" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L49" s="0" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="50">
@@ -2074,7 +2074,7 @@
         <v>2</v>
       </c>
       <c r="C50" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D50" s="0"/>
       <c r="E50" s="0"/>
@@ -2099,16 +2099,16 @@
         <v>25</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C51" s="0">
         <v>1</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E51" s="0" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F51" s="0" t="s">
         <v>109</v>
@@ -2127,7 +2127,7 @@
         <v>120</v>
       </c>
       <c r="L51" s="0" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="52">
@@ -2138,7 +2138,7 @@
         <v>2</v>
       </c>
       <c r="C52" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D52" s="0"/>
       <c r="E52" s="0"/>
@@ -2163,16 +2163,16 @@
         <v>26</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C53" s="0">
         <v>1</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E53" s="0" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="F53" s="0" t="s">
         <v>109</v>
@@ -2188,10 +2188,10 @@
         <v>115</v>
       </c>
       <c r="K53" s="0" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L53" s="0" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="54">
@@ -2233,10 +2233,10 @@
         <v>1</v>
       </c>
       <c r="D55" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E55" s="0" t="s">
-        <v>33</v>
+        <v>77</v>
       </c>
       <c r="F55" s="0" t="s">
         <v>109</v>
@@ -2255,7 +2255,7 @@
         <v>118</v>
       </c>
       <c r="L55" s="0" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="56">
@@ -2266,7 +2266,7 @@
         <v>2</v>
       </c>
       <c r="C56" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D56" s="0"/>
       <c r="E56" s="0"/>
@@ -2297,10 +2297,10 @@
         <v>1</v>
       </c>
       <c r="D57" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E57" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F57" s="0" t="s">
         <v>109</v>
@@ -2316,10 +2316,10 @@
         <v>116</v>
       </c>
       <c r="K57" s="0" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L57" s="0" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="58">
@@ -2361,10 +2361,10 @@
         <v>1</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E59" s="0" t="s">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="F59" s="0" t="s">
         <v>109</v>
@@ -2377,13 +2377,13 @@
         <v>113</v>
       </c>
       <c r="J59" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K59" s="0" t="s">
         <v>119</v>
       </c>
       <c r="L59" s="0" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="60">
@@ -2419,16 +2419,16 @@
         <v>30</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C61" s="0">
         <v>1</v>
       </c>
       <c r="D61" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E61" s="0" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="F61" s="0" t="s">
         <v>109</v>
@@ -2444,10 +2444,10 @@
         <v>115</v>
       </c>
       <c r="K61" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L61" s="0" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="62">
@@ -2458,7 +2458,7 @@
         <v>2</v>
       </c>
       <c r="C62" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D62" s="0"/>
       <c r="E62" s="0"/>
@@ -2483,16 +2483,16 @@
         <v>31</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C63" s="0">
         <v>1</v>
       </c>
       <c r="D63" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E63" s="0" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F63" s="0" t="s">
         <v>109</v>
@@ -2505,13 +2505,13 @@
         <v>113</v>
       </c>
       <c r="J63" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K63" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L63" s="0" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="64">
@@ -2547,16 +2547,16 @@
         <v>32</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C65" s="0">
         <v>1</v>
       </c>
       <c r="D65" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E65" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F65" s="0" t="s">
         <v>109</v>
@@ -2586,7 +2586,7 @@
         <v>2</v>
       </c>
       <c r="C66" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D66" s="0"/>
       <c r="E66" s="0"/>
@@ -2611,16 +2611,16 @@
         <v>33</v>
       </c>
       <c r="B67" s="0" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C67" s="0">
         <v>1</v>
       </c>
       <c r="D67" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E67" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F67" s="0" t="s">
         <v>109</v>
@@ -2636,10 +2636,10 @@
         <v>116</v>
       </c>
       <c r="K67" s="0" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L67" s="0" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
     </row>
     <row r="68">
@@ -2675,16 +2675,16 @@
         <v>34</v>
       </c>
       <c r="B69" s="0" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C69" s="0">
         <v>1</v>
       </c>
       <c r="D69" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E69" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F69" s="0" t="s">
         <v>109</v>
@@ -2700,10 +2700,10 @@
         <v>116</v>
       </c>
       <c r="K69" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L69" s="0" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
     </row>
     <row r="70">
@@ -2739,16 +2739,16 @@
         <v>35</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C71" s="0">
         <v>1</v>
       </c>
       <c r="D71" s="0" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E71" s="0" t="s">
-        <v>98</v>
+        <v>56</v>
       </c>
       <c r="F71" s="0" t="s">
         <v>109</v>
@@ -2764,10 +2764,10 @@
         <v>115</v>
       </c>
       <c r="K71" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L71" s="0" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="72">
@@ -2803,16 +2803,16 @@
         <v>36</v>
       </c>
       <c r="B73" s="0" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C73" s="0">
         <v>1</v>
       </c>
       <c r="D73" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E73" s="0" t="s">
-        <v>45</v>
+        <v>99</v>
       </c>
       <c r="F73" s="0" t="s">
         <v>109</v>
@@ -2825,13 +2825,13 @@
         <v>113</v>
       </c>
       <c r="J73" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K73" s="0" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L73" s="0" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
     </row>
     <row r="74">
@@ -2842,7 +2842,7 @@
         <v>2</v>
       </c>
       <c r="C74" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D74" s="0"/>
       <c r="E74" s="0"/>
@@ -2873,10 +2873,10 @@
         <v>1</v>
       </c>
       <c r="D75" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E75" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F75" s="0" t="s">
         <v>109</v>
@@ -2892,10 +2892,10 @@
         <v>116</v>
       </c>
       <c r="K75" s="0" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L75" s="0" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
     </row>
     <row r="76">
@@ -2906,7 +2906,7 @@
         <v>2</v>
       </c>
       <c r="C76" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D76" s="0"/>
       <c r="E76" s="0"/>
@@ -2931,16 +2931,16 @@
         <v>38</v>
       </c>
       <c r="B77" s="0" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C77" s="0">
         <v>1</v>
       </c>
       <c r="D77" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E77" s="0" t="s">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="F77" s="0" t="s">
         <v>109</v>
@@ -2956,10 +2956,10 @@
         <v>115</v>
       </c>
       <c r="K77" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L77" s="0" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="78">
@@ -2995,16 +2995,16 @@
         <v>39</v>
       </c>
       <c r="B79" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C79" s="0">
         <v>1</v>
       </c>
       <c r="D79" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E79" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F79" s="0" t="s">
         <v>109</v>
@@ -3023,7 +3023,7 @@
         <v>118</v>
       </c>
       <c r="L79" s="0" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="80">
@@ -3059,16 +3059,16 @@
         <v>40</v>
       </c>
       <c r="B81" s="0" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C81" s="0">
         <v>1</v>
       </c>
       <c r="D81" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E81" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F81" s="0" t="s">
         <v>109</v>
@@ -3084,10 +3084,10 @@
         <v>116</v>
       </c>
       <c r="K81" s="0" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L81" s="0" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
     </row>
     <row r="82">
@@ -3098,7 +3098,7 @@
         <v>2</v>
       </c>
       <c r="C82" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D82" s="0"/>
       <c r="E82" s="0"/>
@@ -3123,7 +3123,7 @@
         <v>41</v>
       </c>
       <c r="B83" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C83" s="0">
         <v>1</v>
@@ -3132,26 +3132,26 @@
         <v>50</v>
       </c>
       <c r="E83" s="0" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="F83" s="0" t="s">
         <v>109</v>
       </c>
       <c r="G83" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H83" s="0"/>
       <c r="I83" s="0" t="s">
         <v>113</v>
       </c>
       <c r="J83" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K83" s="0" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L83" s="0" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="84">
@@ -3187,7 +3187,7 @@
         <v>42</v>
       </c>
       <c r="B85" s="0" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C85" s="0">
         <v>1</v>
@@ -3196,7 +3196,7 @@
         <v>51</v>
       </c>
       <c r="E85" s="0" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="F85" s="0" t="s">
         <v>109</v>
@@ -3212,10 +3212,10 @@
         <v>115</v>
       </c>
       <c r="K85" s="0" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L85" s="0" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
     </row>
     <row r="86">
@@ -3251,7 +3251,7 @@
         <v>43</v>
       </c>
       <c r="B87" s="0" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C87" s="0">
         <v>1</v>
@@ -3260,7 +3260,7 @@
         <v>52</v>
       </c>
       <c r="E87" s="0" t="s">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="F87" s="0" t="s">
         <v>109</v>
@@ -3273,13 +3273,13 @@
         <v>113</v>
       </c>
       <c r="J87" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K87" s="0" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L87" s="0" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
     </row>
     <row r="88">
@@ -3315,7 +3315,7 @@
         <v>44</v>
       </c>
       <c r="B89" s="0" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C89" s="0">
         <v>1</v>
@@ -3324,7 +3324,7 @@
         <v>53</v>
       </c>
       <c r="E89" s="0" t="s">
-        <v>93</v>
+        <v>53</v>
       </c>
       <c r="F89" s="0" t="s">
         <v>109</v>
@@ -3337,13 +3337,13 @@
         <v>113</v>
       </c>
       <c r="J89" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K89" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L89" s="0" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
     </row>
     <row r="90">
@@ -3354,7 +3354,7 @@
         <v>2</v>
       </c>
       <c r="C90" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D90" s="0"/>
       <c r="E90" s="0"/>
@@ -3379,7 +3379,7 @@
         <v>45</v>
       </c>
       <c r="B91" s="0" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C91" s="0">
         <v>1</v>
@@ -3388,7 +3388,7 @@
         <v>54</v>
       </c>
       <c r="E91" s="0" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="F91" s="0" t="s">
         <v>109</v>
@@ -3401,13 +3401,13 @@
         <v>113</v>
       </c>
       <c r="J91" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K91" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L91" s="0" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="92">
@@ -3443,7 +3443,7 @@
         <v>46</v>
       </c>
       <c r="B93" s="0" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C93" s="0">
         <v>1</v>
@@ -3468,10 +3468,10 @@
         <v>116</v>
       </c>
       <c r="K93" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L93" s="0" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="94">
@@ -3507,7 +3507,7 @@
         <v>47</v>
       </c>
       <c r="B95" s="0" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C95" s="0">
         <v>1</v>
@@ -3516,7 +3516,7 @@
         <v>56</v>
       </c>
       <c r="E95" s="0" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="F95" s="0" t="s">
         <v>109</v>
@@ -3529,13 +3529,13 @@
         <v>113</v>
       </c>
       <c r="J95" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K95" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L95" s="0" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="96">
@@ -3571,7 +3571,7 @@
         <v>48</v>
       </c>
       <c r="B97" s="0" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C97" s="0">
         <v>1</v>
@@ -3599,7 +3599,7 @@
         <v>120</v>
       </c>
       <c r="L97" s="0" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
     </row>
     <row r="98">
@@ -3635,7 +3635,7 @@
         <v>49</v>
       </c>
       <c r="B99" s="0" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C99" s="0">
         <v>1</v>
@@ -3644,7 +3644,7 @@
         <v>58</v>
       </c>
       <c r="E99" s="0" t="s">
-        <v>23</v>
+        <v>95</v>
       </c>
       <c r="F99" s="0" t="s">
         <v>109</v>
@@ -3660,10 +3660,10 @@
         <v>115</v>
       </c>
       <c r="K99" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L99" s="0" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
     </row>
     <row r="100">
@@ -3699,7 +3699,7 @@
         <v>50</v>
       </c>
       <c r="B101" s="0" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C101" s="0">
         <v>1</v>
@@ -3708,7 +3708,7 @@
         <v>59</v>
       </c>
       <c r="E101" s="0" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F101" s="0" t="s">
         <v>109</v>
@@ -3727,7 +3727,7 @@
         <v>119</v>
       </c>
       <c r="L101" s="0" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
     </row>
     <row r="102">
@@ -3772,7 +3772,7 @@
         <v>60</v>
       </c>
       <c r="E103" s="0" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="F103" s="0" t="s">
         <v>109</v>
@@ -3785,13 +3785,13 @@
         <v>113</v>
       </c>
       <c r="J103" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K103" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L103" s="0" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="104">
@@ -3836,7 +3836,7 @@
         <v>61</v>
       </c>
       <c r="E105" s="0" t="s">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="F105" s="0" t="s">
         <v>109</v>
@@ -3849,13 +3849,13 @@
         <v>113</v>
       </c>
       <c r="J105" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K105" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L105" s="0" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
     </row>
     <row r="106">
@@ -3866,7 +3866,7 @@
         <v>2</v>
       </c>
       <c r="C106" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D106" s="0"/>
       <c r="E106" s="0"/>
@@ -3891,7 +3891,7 @@
         <v>53</v>
       </c>
       <c r="B107" s="0" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C107" s="0">
         <v>1</v>
@@ -3900,7 +3900,7 @@
         <v>62</v>
       </c>
       <c r="E107" s="0" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="F107" s="0" t="s">
         <v>109</v>
@@ -3913,13 +3913,13 @@
         <v>113</v>
       </c>
       <c r="J107" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K107" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L107" s="0" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="108">
@@ -3930,7 +3930,7 @@
         <v>2</v>
       </c>
       <c r="C108" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D108" s="0"/>
       <c r="E108" s="0"/>
@@ -3955,7 +3955,7 @@
         <v>54</v>
       </c>
       <c r="B109" s="0" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C109" s="0">
         <v>1</v>
@@ -3964,7 +3964,7 @@
         <v>63</v>
       </c>
       <c r="E109" s="0" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="F109" s="0" t="s">
         <v>109</v>
@@ -3980,10 +3980,10 @@
         <v>115</v>
       </c>
       <c r="K109" s="0" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L109" s="0" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
     </row>
     <row r="110">
@@ -3994,7 +3994,7 @@
         <v>2</v>
       </c>
       <c r="C110" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D110" s="0"/>
       <c r="E110" s="0"/>
@@ -4019,7 +4019,7 @@
         <v>55</v>
       </c>
       <c r="B111" s="0" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C111" s="0">
         <v>1</v>
@@ -4028,7 +4028,7 @@
         <v>64</v>
       </c>
       <c r="E111" s="0" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="F111" s="0" t="s">
         <v>109</v>
@@ -4041,13 +4041,13 @@
         <v>113</v>
       </c>
       <c r="J111" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K111" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L111" s="0" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="112">
@@ -4083,7 +4083,7 @@
         <v>56</v>
       </c>
       <c r="B113" s="0" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C113" s="0">
         <v>1</v>
@@ -4111,7 +4111,7 @@
         <v>119</v>
       </c>
       <c r="L113" s="0" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="114">
@@ -4122,7 +4122,7 @@
         <v>2</v>
       </c>
       <c r="C114" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D114" s="0"/>
       <c r="E114" s="0"/>
@@ -4147,7 +4147,7 @@
         <v>57</v>
       </c>
       <c r="B115" s="0" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C115" s="0">
         <v>1</v>
@@ -4156,7 +4156,7 @@
         <v>66</v>
       </c>
       <c r="E115" s="0" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="F115" s="0" t="s">
         <v>109</v>
@@ -4169,13 +4169,13 @@
         <v>113</v>
       </c>
       <c r="J115" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K115" s="0" t="s">
         <v>120</v>
       </c>
       <c r="L115" s="0" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="116">
@@ -4186,7 +4186,7 @@
         <v>2</v>
       </c>
       <c r="C116" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D116" s="0"/>
       <c r="E116" s="0"/>
@@ -4211,7 +4211,7 @@
         <v>58</v>
       </c>
       <c r="B117" s="0" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C117" s="0">
         <v>1</v>
@@ -4239,7 +4239,7 @@
         <v>120</v>
       </c>
       <c r="L117" s="0" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="118">
@@ -4275,7 +4275,7 @@
         <v>59</v>
       </c>
       <c r="B119" s="0" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C119" s="0">
         <v>1</v>
@@ -4284,7 +4284,7 @@
         <v>68</v>
       </c>
       <c r="E119" s="0" t="s">
-        <v>52</v>
+        <v>97</v>
       </c>
       <c r="F119" s="0" t="s">
         <v>109</v>
@@ -4300,10 +4300,10 @@
         <v>115</v>
       </c>
       <c r="K119" s="0" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L119" s="0" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
     </row>
     <row r="120">
@@ -4314,7 +4314,7 @@
         <v>2</v>
       </c>
       <c r="C120" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D120" s="0"/>
       <c r="E120" s="0"/>
@@ -4339,7 +4339,7 @@
         <v>60</v>
       </c>
       <c r="B121" s="0" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C121" s="0">
         <v>1</v>
@@ -4367,7 +4367,7 @@
         <v>119</v>
       </c>
       <c r="L121" s="0" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
     </row>
     <row r="122">
@@ -4378,7 +4378,7 @@
         <v>2</v>
       </c>
       <c r="C122" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D122" s="0"/>
       <c r="E122" s="0"/>
@@ -4412,7 +4412,7 @@
         <v>70</v>
       </c>
       <c r="E123" s="0" t="s">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="F123" s="0" t="s">
         <v>109</v>
@@ -4425,13 +4425,13 @@
         <v>113</v>
       </c>
       <c r="J123" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K123" s="0" t="s">
         <v>119</v>
       </c>
       <c r="L123" s="0" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="124">
@@ -4442,7 +4442,7 @@
         <v>2</v>
       </c>
       <c r="C124" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D124" s="0"/>
       <c r="E124" s="0"/>
@@ -4467,7 +4467,7 @@
         <v>62</v>
       </c>
       <c r="B125" s="0" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C125" s="0">
         <v>1</v>
@@ -4476,7 +4476,7 @@
         <v>71</v>
       </c>
       <c r="E125" s="0" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="F125" s="0" t="s">
         <v>109</v>
@@ -4489,13 +4489,13 @@
         <v>113</v>
       </c>
       <c r="J125" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K125" s="0" t="s">
         <v>118</v>
       </c>
       <c r="L125" s="0" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
     </row>
     <row r="126">
@@ -4506,7 +4506,7 @@
         <v>2</v>
       </c>
       <c r="C126" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D126" s="0"/>
       <c r="E126" s="0"/>
@@ -4531,7 +4531,7 @@
         <v>63</v>
       </c>
       <c r="B127" s="0" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C127" s="0">
         <v>1</v>
@@ -4540,7 +4540,7 @@
         <v>72</v>
       </c>
       <c r="E127" s="0" t="s">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="F127" s="0" t="s">
         <v>109</v>
@@ -4556,10 +4556,10 @@
         <v>115</v>
       </c>
       <c r="K127" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L127" s="0" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="128">
@@ -4570,7 +4570,7 @@
         <v>2</v>
       </c>
       <c r="C128" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D128" s="0"/>
       <c r="E128" s="0"/>
@@ -4595,7 +4595,7 @@
         <v>64</v>
       </c>
       <c r="B129" s="0" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C129" s="0">
         <v>1</v>
@@ -4620,10 +4620,10 @@
         <v>116</v>
       </c>
       <c r="K129" s="0" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L129" s="0" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="130">
@@ -4634,7 +4634,7 @@
         <v>2</v>
       </c>
       <c r="C130" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D130" s="0"/>
       <c r="E130" s="0"/>
@@ -4659,7 +4659,7 @@
         <v>65</v>
       </c>
       <c r="B131" s="0" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C131" s="0">
         <v>1</v>
@@ -4668,7 +4668,7 @@
         <v>74</v>
       </c>
       <c r="E131" s="0" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="F131" s="0" t="s">
         <v>109</v>
@@ -4684,10 +4684,10 @@
         <v>115</v>
       </c>
       <c r="K131" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L131" s="0" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="132">
@@ -4723,7 +4723,7 @@
         <v>66</v>
       </c>
       <c r="B133" s="0" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C133" s="0">
         <v>1</v>
@@ -4732,7 +4732,7 @@
         <v>75</v>
       </c>
       <c r="E133" s="0" t="s">
-        <v>69</v>
+        <v>19</v>
       </c>
       <c r="F133" s="0" t="s">
         <v>109</v>
@@ -4748,10 +4748,10 @@
         <v>115</v>
       </c>
       <c r="K133" s="0" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L133" s="0" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
     </row>
     <row r="134">
@@ -4787,7 +4787,7 @@
         <v>67</v>
       </c>
       <c r="B135" s="0" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C135" s="0">
         <v>1</v>
@@ -4796,7 +4796,7 @@
         <v>76</v>
       </c>
       <c r="E135" s="0" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="F135" s="0" t="s">
         <v>109</v>
@@ -4809,13 +4809,13 @@
         <v>113</v>
       </c>
       <c r="J135" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K135" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L135" s="0" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="136">
@@ -4851,7 +4851,7 @@
         <v>68</v>
       </c>
       <c r="B137" s="0" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C137" s="0">
         <v>1</v>
@@ -4860,7 +4860,7 @@
         <v>77</v>
       </c>
       <c r="E137" s="0" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="F137" s="0" t="s">
         <v>109</v>
@@ -4873,13 +4873,13 @@
         <v>113</v>
       </c>
       <c r="J137" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K137" s="0" t="s">
         <v>118</v>
       </c>
       <c r="L137" s="0" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="138">
@@ -4890,7 +4890,7 @@
         <v>2</v>
       </c>
       <c r="C138" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D138" s="0"/>
       <c r="E138" s="0"/>
@@ -4915,7 +4915,7 @@
         <v>69</v>
       </c>
       <c r="B139" s="0" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C139" s="0">
         <v>1</v>
@@ -4924,7 +4924,7 @@
         <v>78</v>
       </c>
       <c r="E139" s="0" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="F139" s="0" t="s">
         <v>109</v>
@@ -4937,13 +4937,13 @@
         <v>113</v>
       </c>
       <c r="J139" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K139" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L139" s="0" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
     </row>
     <row r="140">
@@ -4988,7 +4988,7 @@
         <v>79</v>
       </c>
       <c r="E141" s="0" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="F141" s="0" t="s">
         <v>109</v>
@@ -5001,13 +5001,13 @@
         <v>113</v>
       </c>
       <c r="J141" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K141" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L141" s="0" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
     </row>
     <row r="142">
@@ -5043,7 +5043,7 @@
         <v>71</v>
       </c>
       <c r="B143" s="0" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C143" s="0">
         <v>1</v>
@@ -5052,7 +5052,7 @@
         <v>80</v>
       </c>
       <c r="E143" s="0" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="F143" s="0" t="s">
         <v>109</v>
@@ -5065,10 +5065,10 @@
         <v>113</v>
       </c>
       <c r="J143" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K143" s="0" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L143" s="0" t="s">
         <v>138</v>
@@ -5107,35 +5107,35 @@
         <v>72</v>
       </c>
       <c r="B145" s="0" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C145" s="0">
         <v>1</v>
       </c>
       <c r="D145" s="0" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E145" s="0" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="F145" s="0" t="s">
         <v>109</v>
       </c>
       <c r="G145" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H145" s="0"/>
       <c r="I145" s="0" t="s">
         <v>113</v>
       </c>
       <c r="J145" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K145" s="0" t="s">
         <v>118</v>
       </c>
       <c r="L145" s="0" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
     </row>
     <row r="146">
@@ -5177,10 +5177,10 @@
         <v>1</v>
       </c>
       <c r="D147" s="0" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E147" s="0" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="F147" s="0" t="s">
         <v>109</v>
@@ -5193,13 +5193,13 @@
         <v>113</v>
       </c>
       <c r="J147" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K147" s="0" t="s">
         <v>120</v>
       </c>
       <c r="L147" s="0" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="148">
@@ -5210,7 +5210,7 @@
         <v>2</v>
       </c>
       <c r="C148" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D148" s="0"/>
       <c r="E148" s="0"/>
@@ -5235,16 +5235,16 @@
         <v>74</v>
       </c>
       <c r="B149" s="0" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C149" s="0">
         <v>1</v>
       </c>
       <c r="D149" s="0" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E149" s="0" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="F149" s="0" t="s">
         <v>109</v>
@@ -5257,13 +5257,13 @@
         <v>113</v>
       </c>
       <c r="J149" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K149" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L149" s="0" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
     </row>
     <row r="150">
@@ -5274,7 +5274,7 @@
         <v>2</v>
       </c>
       <c r="C150" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D150" s="0"/>
       <c r="E150" s="0"/>
@@ -5299,16 +5299,16 @@
         <v>75</v>
       </c>
       <c r="B151" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C151" s="0">
         <v>1</v>
       </c>
       <c r="D151" s="0" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E151" s="0" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F151" s="0" t="s">
         <v>109</v>
@@ -5324,10 +5324,10 @@
         <v>116</v>
       </c>
       <c r="K151" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L151" s="0" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
     </row>
     <row r="152">
@@ -5369,10 +5369,10 @@
         <v>1</v>
       </c>
       <c r="D153" s="0" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E153" s="0" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F153" s="0" t="s">
         <v>109</v>
@@ -5388,10 +5388,10 @@
         <v>116</v>
       </c>
       <c r="K153" s="0" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L153" s="0" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="154">
@@ -5402,7 +5402,7 @@
         <v>2</v>
       </c>
       <c r="C154" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D154" s="0"/>
       <c r="E154" s="0"/>
@@ -5427,16 +5427,16 @@
         <v>77</v>
       </c>
       <c r="B155" s="0" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C155" s="0">
         <v>1</v>
       </c>
       <c r="D155" s="0" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E155" s="0" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F155" s="0" t="s">
         <v>109</v>
@@ -5452,7 +5452,7 @@
         <v>115</v>
       </c>
       <c r="K155" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L155" s="0" t="s">
         <v>129</v>
@@ -5497,10 +5497,10 @@
         <v>1</v>
       </c>
       <c r="D157" s="0" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E157" s="0" t="s">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="F157" s="0" t="s">
         <v>109</v>
@@ -5513,13 +5513,13 @@
         <v>113</v>
       </c>
       <c r="J157" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K157" s="0" t="s">
         <v>120</v>
       </c>
       <c r="L157" s="0" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="158">
@@ -5555,16 +5555,16 @@
         <v>79</v>
       </c>
       <c r="B159" s="0" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C159" s="0">
         <v>1</v>
       </c>
       <c r="D159" s="0" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E159" s="0" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="F159" s="0" t="s">
         <v>109</v>
@@ -5577,13 +5577,13 @@
         <v>113</v>
       </c>
       <c r="J159" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K159" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L159" s="0" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
     </row>
     <row r="160">
@@ -5594,7 +5594,7 @@
         <v>2</v>
       </c>
       <c r="C160" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D160" s="0"/>
       <c r="E160" s="0"/>
@@ -5619,16 +5619,16 @@
         <v>80</v>
       </c>
       <c r="B161" s="0" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C161" s="0">
         <v>1</v>
       </c>
       <c r="D161" s="0" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E161" s="0" t="s">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="F161" s="0" t="s">
         <v>109</v>
@@ -5641,13 +5641,13 @@
         <v>113</v>
       </c>
       <c r="J161" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K161" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L161" s="0" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="162">
@@ -5683,16 +5683,16 @@
         <v>81</v>
       </c>
       <c r="B163" s="0" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C163" s="0">
         <v>1</v>
       </c>
       <c r="D163" s="0" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E163" s="0" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="F163" s="0" t="s">
         <v>109</v>
@@ -5708,10 +5708,10 @@
         <v>115</v>
       </c>
       <c r="K163" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L163" s="0" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="164">
@@ -5747,16 +5747,16 @@
         <v>82</v>
       </c>
       <c r="B165" s="0" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C165" s="0">
         <v>1</v>
       </c>
       <c r="D165" s="0" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E165" s="0" t="s">
-        <v>105</v>
+        <v>62</v>
       </c>
       <c r="F165" s="0" t="s">
         <v>109</v>
@@ -5775,7 +5775,7 @@
         <v>119</v>
       </c>
       <c r="L165" s="0" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
     </row>
     <row r="166">
@@ -5811,16 +5811,16 @@
         <v>83</v>
       </c>
       <c r="B167" s="0" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C167" s="0">
         <v>1</v>
       </c>
       <c r="D167" s="0" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E167" s="0" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="F167" s="0" t="s">
         <v>109</v>
@@ -5833,13 +5833,13 @@
         <v>113</v>
       </c>
       <c r="J167" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K167" s="0" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L167" s="0" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="168">
@@ -5875,16 +5875,16 @@
         <v>84</v>
       </c>
       <c r="B169" s="0" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C169" s="0">
         <v>1</v>
       </c>
       <c r="D169" s="0" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E169" s="0" t="s">
-        <v>93</v>
+        <v>54</v>
       </c>
       <c r="F169" s="0" t="s">
         <v>109</v>
@@ -5897,13 +5897,13 @@
         <v>113</v>
       </c>
       <c r="J169" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K169" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L169" s="0" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
     </row>
     <row r="170">
@@ -5939,16 +5939,16 @@
         <v>85</v>
       </c>
       <c r="B171" s="0" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C171" s="0">
         <v>1</v>
       </c>
       <c r="D171" s="0" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E171" s="0" t="s">
-        <v>29</v>
+        <v>93</v>
       </c>
       <c r="F171" s="0" t="s">
         <v>109</v>
@@ -5961,13 +5961,13 @@
         <v>113</v>
       </c>
       <c r="J171" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K171" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L171" s="0" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="172">
@@ -5978,7 +5978,7 @@
         <v>2</v>
       </c>
       <c r="C172" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D172" s="0"/>
       <c r="E172" s="0"/>
@@ -6003,16 +6003,16 @@
         <v>86</v>
       </c>
       <c r="B173" s="0" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C173" s="0">
         <v>1</v>
       </c>
       <c r="D173" s="0" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E173" s="0" t="s">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="F173" s="0" t="s">
         <v>109</v>
@@ -6025,13 +6025,13 @@
         <v>113</v>
       </c>
       <c r="J173" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K173" s="0" t="s">
         <v>118</v>
       </c>
       <c r="L173" s="0" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
     </row>
     <row r="174">
@@ -6073,10 +6073,10 @@
         <v>1</v>
       </c>
       <c r="D175" s="0" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E175" s="0" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="F175" s="0" t="s">
         <v>109</v>
@@ -6089,7 +6089,7 @@
         <v>113</v>
       </c>
       <c r="J175" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K175" s="0" t="s">
         <v>120</v>
@@ -6131,7 +6131,7 @@
         <v>88</v>
       </c>
       <c r="B177" s="0" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C177" s="0">
         <v>1</v>
@@ -6140,23 +6140,23 @@
         <v>96</v>
       </c>
       <c r="E177" s="0" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="F177" s="0" t="s">
         <v>109</v>
       </c>
       <c r="G177" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H177" s="0"/>
       <c r="I177" s="0" t="s">
         <v>113</v>
       </c>
       <c r="J177" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K177" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L177" s="0" t="s">
         <v>137</v>
@@ -6170,7 +6170,7 @@
         <v>2</v>
       </c>
       <c r="C178" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D178" s="0"/>
       <c r="E178" s="0"/>
@@ -6195,7 +6195,7 @@
         <v>89</v>
       </c>
       <c r="B179" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C179" s="0">
         <v>1</v>
@@ -6223,7 +6223,7 @@
         <v>118</v>
       </c>
       <c r="L179" s="0" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="180">
@@ -6259,7 +6259,7 @@
         <v>90</v>
       </c>
       <c r="B181" s="0" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C181" s="0">
         <v>1</v>
@@ -6268,7 +6268,7 @@
         <v>98</v>
       </c>
       <c r="E181" s="0" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="F181" s="0" t="s">
         <v>109</v>
@@ -6281,13 +6281,13 @@
         <v>113</v>
       </c>
       <c r="J181" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K181" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L181" s="0" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="182">
@@ -6298,7 +6298,7 @@
         <v>2</v>
       </c>
       <c r="C182" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D182" s="0"/>
       <c r="E182" s="0"/>
@@ -6323,7 +6323,7 @@
         <v>91</v>
       </c>
       <c r="B183" s="0" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C183" s="0">
         <v>1</v>
@@ -6348,10 +6348,10 @@
         <v>116</v>
       </c>
       <c r="K183" s="0" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L183" s="0" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="184">
@@ -6362,7 +6362,7 @@
         <v>2</v>
       </c>
       <c r="C184" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D184" s="0"/>
       <c r="E184" s="0"/>
@@ -6387,7 +6387,7 @@
         <v>92</v>
       </c>
       <c r="B185" s="0" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C185" s="0">
         <v>1</v>
@@ -6396,7 +6396,7 @@
         <v>100</v>
       </c>
       <c r="E185" s="0" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="F185" s="0" t="s">
         <v>109</v>
@@ -6412,10 +6412,10 @@
         <v>115</v>
       </c>
       <c r="K185" s="0" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L185" s="0" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="186">
@@ -6426,7 +6426,7 @@
         <v>2</v>
       </c>
       <c r="C186" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D186" s="0"/>
       <c r="E186" s="0"/>
@@ -6451,7 +6451,7 @@
         <v>93</v>
       </c>
       <c r="B187" s="0" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C187" s="0">
         <v>1</v>
@@ -6460,7 +6460,7 @@
         <v>101</v>
       </c>
       <c r="E187" s="0" t="s">
-        <v>14</v>
+        <v>101</v>
       </c>
       <c r="F187" s="0" t="s">
         <v>109</v>
@@ -6473,10 +6473,10 @@
         <v>113</v>
       </c>
       <c r="J187" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K187" s="0" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L187" s="0" t="s">
         <v>126</v>
@@ -6490,7 +6490,7 @@
         <v>2</v>
       </c>
       <c r="C188" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D188" s="0"/>
       <c r="E188" s="0"/>
@@ -6515,7 +6515,7 @@
         <v>94</v>
       </c>
       <c r="B189" s="0" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C189" s="0">
         <v>1</v>
@@ -6543,7 +6543,7 @@
         <v>119</v>
       </c>
       <c r="L189" s="0" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
     </row>
     <row r="190">
@@ -6554,7 +6554,7 @@
         <v>2</v>
       </c>
       <c r="C190" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D190" s="0"/>
       <c r="E190" s="0"/>
@@ -6579,7 +6579,7 @@
         <v>95</v>
       </c>
       <c r="B191" s="0" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C191" s="0">
         <v>1</v>
@@ -6588,7 +6588,7 @@
         <v>103</v>
       </c>
       <c r="E191" s="0" t="s">
-        <v>65</v>
+        <v>102</v>
       </c>
       <c r="F191" s="0" t="s">
         <v>109</v>
@@ -6607,7 +6607,7 @@
         <v>119</v>
       </c>
       <c r="L191" s="0" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="192">
@@ -6652,7 +6652,7 @@
         <v>104</v>
       </c>
       <c r="E193" s="0" t="s">
-        <v>104</v>
+        <v>57</v>
       </c>
       <c r="F193" s="0" t="s">
         <v>109</v>
@@ -6665,10 +6665,10 @@
         <v>113</v>
       </c>
       <c r="J193" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K193" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L193" s="0" t="s">
         <v>124</v>
@@ -6682,7 +6682,7 @@
         <v>2</v>
       </c>
       <c r="C194" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D194" s="0"/>
       <c r="E194" s="0"/>
@@ -6707,7 +6707,7 @@
         <v>97</v>
       </c>
       <c r="B195" s="0" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C195" s="0">
         <v>1</v>
@@ -6735,7 +6735,7 @@
         <v>119</v>
       </c>
       <c r="L195" s="0" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
     </row>
     <row r="196">
@@ -6771,7 +6771,7 @@
         <v>98</v>
       </c>
       <c r="B197" s="0" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C197" s="0">
         <v>1</v>
@@ -6799,7 +6799,7 @@
         <v>120</v>
       </c>
       <c r="L197" s="0" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="198">
